--- a/outreach_tracker.xlsx
+++ b/outreach_tracker.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Outreach Tracker" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Competitors Researched" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Full Backlink Triage" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -905,22 +906,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>N/A - needs research</t>
+          <t>Vince Battaglia</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>info@thetradeshowcalendar.com</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>(see Orbus row)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Researched - not drafted</t>
+          <t>Sent - duplicate of Orbus row</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
@@ -1188,31 +1189,39 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>PR / Press mention</t>
+          <t>PR / Source + contributed how-to</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Jeff Wooten (Editor)</t>
+          <t>Alex Marcheschi (Editor-in-Chief)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Not confirmed - site blocks scraping</t>
+          <t>amarcheschi@sbpub.com</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Trade show graphics how-to - source or contributed tip for SBI</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Researched - no verified email yet</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>marketing@apextradeshow.com</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
           <t>Real monthly sign industry trade magazine, covers industry news/product releases; call main office to get direct editorial email</t>
@@ -1242,21 +1251,29 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>No email found - phone (702) 839-8181</t>
+          <t>info@thetradeshowcalendar.com</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Partner listing for a trade show graphics printer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Researched - phone contact only</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>marketing@apextradeshow.com</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
           <t>B2B trade show directory, appeared as a referrer for both Nimlok and Expo Marketing - worth a phone call, no public email</t>
@@ -1372,31 +1389,39 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>PR / Press mention</t>
+          <t>PR / Source relationship</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Sarah Kloepple (Deputy Editor) + team</t>
+          <t>Editorial team</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Email is Cloudflare-obfuscated, not confirmed</t>
+          <t>editorial@bizbash.com</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Production-side source for event design and fabrication stories</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Researched - no verified email yet</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>marketing@apextradeshow.com</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
           <t>Major event industry trade publication (Fanatics Fest 2026 coverage); pitches must tie to a specific event within 2 weeks of it happening</t>
@@ -1426,21 +1451,29 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Email is Cloudflare-obfuscated, not confirmed</t>
+          <t>Contact form (clearviewtvmirror.com/contact)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Contact form: cross-referral / mutual resource mention</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Researched - no verified email yet</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
+          <t>Sent via contact form</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>marketing@apextradeshow.com</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
           <t>Custom mirror TV/AV manufacturer for booths - complementary hardware, phone (888) 343-4665 available as fallback</t>
@@ -1644,6 +1677,738 @@
       <c r="J25" t="inlineStr">
         <is>
           <t>High-authority (DR90) vetted agency directory with a 'Submit An Agency' application process at designrush.com/submit/agency - not an email pitch, needs Manish to apply with portfolio/business info</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Classic Exhibits</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>bluleadz.com</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Backlink partnership</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Contact form (bluleadz.com/contact-bluleadz)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Contact form: printing-side tip / link exchange</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Sent via contact form</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>marketing@apextradeshow.com</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Marketing agency, '20 Trade Show Marketing Ideas' post; bluleadz.com/contact-bluleadz</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>PosterGarden</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>insights4print.ceo</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>PR / Source relationship</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Eddy Hagen</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Contact form (insights4print.ceo/contact)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Print-side perspective from trade show graphics</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Sent via contact form</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>marketing@apextradeshow.com</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Independent print-industry analyst blog (colour management focus)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ExhibitDeal</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>trade-show-advisor.com</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Directory listing / tip</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Contact form with CAPTCHA</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Supplier Directory listing request</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Needs manual submit (CAPTCHA)</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Form at trade-show-advisor.com/trade-show-advisor-contact-form.html requires ticking I'm-not-a-robot - Manish to submit</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Expo Marketing / 3D Exhibits</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>tradeshowlabs.com</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Referral / resource partnership</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>contact@tradeshowlabs.com</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Booth games + booth graphics - referral partnership?</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>marketing@apextradeshow.com</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Trade show games/activations company; email found in site footer</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>GES</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>thelogisticsoflogistics.com</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Source / resource link</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Contact form with CAPTCHA</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Trade show shipping guide - print-side perspective</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Filled - needs manual CAPTCHA + submit</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Form is filled in on an open Chrome tab; Manish just ticks I'm-not-a-robot and clicks Submit</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>BannerBuzz</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>thedisplayshield.com</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Backlink partnership</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Phone only 1-800-331-2628</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Skipped - no email or form</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Contact page lists only a phone number</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Classic Exhibits</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>exhibitoradvocacy.com</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>PR / Source relationship</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Joe Federbush (Founder)</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>info@exhibitoradvocacy.com</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Supporting exhibitor-side transparency - from the print side</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>marketing@apextradeshow.com</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Nonprofit exhibitor advocacy association; pitched as a printing-side source and asked about vendor alignment/listing</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Classic Exhibits</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>scubefixtures.com</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>N/A - competitor</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Skipped - competitor, not a partner</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Actually a portable display/fixture manufacturer competing in adjacent hardware space, not a partnership fit</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Xibit Solutions</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>elev8.la</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Backlink / co-marketing partnership</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Grant Morningstar (CEO)</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>hello@elev8.la</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Booth staffing + booth graphics - referral partnership?</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>REPLIED - wants our service list</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>marketing@apextradeshow.com</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Event staffing/brand ambassador agency (Las Vegas) - complementary, non-competing service for the same exhibitors</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Impact XM</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>eventindustrynews.com</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>PR / Source relationship</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Adam Parry (Editor)</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>editor@eventindustrynews.com</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Printing/production-side source for event industry stories</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>marketing@apextradeshow.com</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>UK event industry trade news site; address came from a search result, not listed on-site - watch for bounce</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Impact XM</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>engine.com</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>PR / Roundup inclusion</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>No form - support chat/phone only</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Skipped - no contact form exists</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Sports event planning roundup; engine.com/contact-us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Impact XM</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>spotme.com</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Referral / resource partnership</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>americas@spotme.com</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Partnership idea: SpotMe events + printed booth graphics</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>marketing@apextradeshow.com</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Enterprise event platform, 'best hybrid event management companies' roundup; spotme.com/contact-us</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Impact XM</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>bizzabo.com</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>PR / Blog feature</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Blog team</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>blog@bizzabo.com</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Feature idea: the printed side of corporate event themes</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>marketing@apextradeshow.com</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Event platform, corporate event themes blog; bizzabo.com/contact-us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Impact XM</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>avenuez.com</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>PR / Roundup inclusion</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Contact form (avenuez.com/contact-us)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Contact form: referral partnership / guide mention</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Sent via contact form</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>marketing@apextradeshow.com</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Beauty/wellness event PR agency, roundup lists Avenue Z itself first; avenuez.com/contact-us</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>3D Exhibits / Expo Marketing</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>wearesparks.com</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>PR / Source relationship</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Kristin Castelli (SVP Strategic Growth)</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Lead form only - no message field</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Skipped - form cannot carry a message</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Global healthcare/experiential brand agency, appeared as referrer for both Expo Marketing and 3D Exhibits; wearesparks.com/contact/</t>
         </is>
       </c>
     </row>
@@ -2098,4 +2863,4195 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E162"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Competitor</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Referring Domain</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>DR</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Disposition</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>bannerbuzz.com</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>bannerbuzz.co.uk / .ca / .com.au / .co.nz</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>20-43</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Competitor's own regional sites</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>bannerbuzz.com</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>vivipins.com</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>54</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Sent (see tracker)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Roundup inclusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>bannerbuzz.com</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>makerflo.com</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>59</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Guest-post target, left to guest-post session</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>bannerbuzz.com</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>bestofsigns.com</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>43</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Competitor - skipped</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sign printer</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>bannerbuzz.com</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>simplycodes.com / savings.com</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>71</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Coupon aggregators</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>bannerbuzz.com</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>dirtamericana.com</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>13</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Unrelated blog (flag lots)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>bannerbuzz.com</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>procoolmfg.com</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>20</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Sent (see tracker)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Partnership</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>bannerbuzz.com</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>bemorekinky.com</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>37</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Adult content - brand risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>bannerbuzz.com</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>secondchanceanimalsorg</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>60</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Nonprofit sponsorship</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>bannerbuzz.com</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>circleone.in</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>26</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Sent (see tracker)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Partnership</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>bannerbuzz.com</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>groovyguygifts.com</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>42</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Guest-post target, left to guest-post session</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>bannerbuzz.com</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>bbb.org</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>93</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Business profile</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>bannerbuzz.com</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>kesem.mit.edu</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>92</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Nonprofit sponsorship</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>bannerbuzz.com</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>thedisplayshield.com</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>14</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Phone only, no email or form</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>bannerbuzz.com</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>groupbayport.com</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>26</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>BannerBuzz parent company</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>bannerbuzz.com</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>vailfucci.com</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>27</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Guest-post target, left to guest-post session</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>buildasign.com</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>easycanvasprints / signsonthecheap</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>41-53</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>BuildASign sister brands</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>buildasign.com</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>exptoolkit / exprealty / kw resources / allcityagents / thinkrealty / whylibertas</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0-83</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Real estate brokerage internal portals</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>buildasign.com</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>couponcabin / savings / simplycodes</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>62-71</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Coupon aggregators</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>buildasign.com</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>themilitarywifeandmom / military.com / seasonedspouse / thebrobasket</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>20-85</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Military free-banner program, audience mismatch</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>buildasign.com</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>homelight.com / listwithclever.com</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>76-79</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Real estate FSBO signs, audience mismatch</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>nimlok.com</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>orbus.com / nimlok.ca / orbusvisualcommunicationsgroup / orbuscanada</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>18-66</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Nimlok parent/sister companies</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>nimlok.com</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>nimloktradeshowmarketing.com</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>52</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Nimlok's own blog</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>nimlok.com</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>therogersco / idec-displays / carolinatradeshowexhibits / tradeshowdisplayoutlet / plumgroveinc</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>0-29</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Competitor - skipped</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Exhibit/display dealers</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>nimlok.com</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>newgennow.com / conventionsuite.com</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>7-31</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Sent (see tracker)</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Partnership (ConventionSuite)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>nimlok.com</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>hubspot checklist PDF</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>75</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Unattributed file</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>nimlok.com</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>thetradeshowcalendar.com</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>28</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Sent (see tracker)</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>info@thetradeshowcalendar.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>nimlok.com</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>grokipedia.com</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>78</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>AI encyclopedia</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>nimlok.com</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>american-image.com</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>43</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Competitor - skipped</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Exhibit company</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>nimlok.com</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>siliconlightworks.com</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>29</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Sent (see tracker)</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Partnership</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>nimlok.com</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>connect2home.org</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>46</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Nonprofit</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>nimlok.com</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>tradetoons.com</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Very low authority</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>nimlok.com</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>edpamidwest.org</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>16</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Member-only association</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>exhibitdeal.com</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>camelotprintandcopy.us</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>26</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Sent (see tracker)</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Roundup inclusion (replied)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>exhibitdeal.com</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>monsterdisplays.com</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>10</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Competitor - skipped</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Display seller</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>exhibitdeal.com</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>pandia / avivadirectory / sitelike / theglobe / abc-directory / laslett / yellowpages / dexknows</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2-89</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Directories</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>exhibitdeal.com</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>copyblogger.com</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>84</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Author bio link only</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>exhibitdeal.com</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>trade-show-advisor.com</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>32</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Needs manual submit</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Form has an I'm-not-a-robot CAPTCHA - Manish must submit</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>exhibitdeal.com</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>virtualvalley.io / crunchbase / owler / articlesurfing / prlog.ru / dacheckeronlinefree</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>0-91</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Profiles, article farms, SEO spam</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>classicexhibits.com</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>thetradeshownetwork.com</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>51</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Competitor - skipped</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Exhibit rental company</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>classicexhibits.com</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>exhibitoradvocacy.com</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>28</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Sent (see tracker)</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Source relationship</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>classicexhibits.com</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>businessanalystlearnings.com</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>40</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Unrelated blog</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>classicexhibits.com</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>businessmanagementreview.com</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>49</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Paid vendor directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>classicexhibits.com</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>exhibitcitynews.com</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>56</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Sent (see tracker)</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Directory listing + source</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>classicexhibits.com</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>fitnyc.edu</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>79</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Internship page</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>classicexhibits.com</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>ecosystemsdisplays / tradegroup / classicmodul</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>13-35</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Competitor - skipped</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Exhibit companies / sister brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>classicexhibits.com</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>bbb.org / feedburner / wp.me</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>91-94</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Profiles/feeds</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>classicexhibits.com</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>tradeshowbestpractices.com</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>7</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Dormant since 2015</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>classicexhibits.com</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>plumgroveinc.com</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>29</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Competitor - skipped</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Graphics replacement supplier</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>classicexhibits.com</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>cmocouncil.org</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>75</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Paid sponsorship</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>classicexhibits.com</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>exhibitoronline.com (Top 40)</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>72</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Invite/evaluation only</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>classicexhibits.com</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>edpanortheast.com</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>10</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Member-only association</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>classicexhibits.com</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>scubefixtures.com</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>24</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Competitor - skipped</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Display manufacturer</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>classicexhibits.com</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>kingwe-star.com / kathrynread.com</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1-34</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Low relevance</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>expomarketing.com</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>proexhibits.com / uspress.com</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>29-32</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Competitor - skipped</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Exhibit/print companies</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>expomarketing.com</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>sockclub.com</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>62</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Sent (see tracker)</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Partnership</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>expomarketing.com</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>kolilazim.com / servicebureau.nl</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2-9</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Foreign-language low authority</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>expomarketing.com</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>thetradeshowcalendar.com</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>28</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Sent (see tracker)</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>info@thetradeshowcalendar.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>expomarketing.com</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>wearesparks.com</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>53</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Lead form only, no message field</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>expomarketing.com</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>lookwhatmomfound / joinjuno / azinstabio / fourmagazine / opgram / grammeroverview / ok-jatt / zenandbusiness / plant-wide</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>19-67</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Link-farm style general blogs</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>expomarketing.com</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>grokipedia / rocketreach</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>76-78</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>AI encyclopedia / data profile</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>expomarketing.com</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>tradeshowlabs.com</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>56</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Sent (see tracker)</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>contact@tradeshowlabs.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>expomarketing.com</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>vdshowcase.com / tradetoons.com</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Very low authority</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>skyline.com</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>gemspring / peninsula-style investor pages</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>42</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Investor portfolio</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>skyline.com</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>knotsoflove.org / worldoutreach.org</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>49-59</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Nonprofits</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>skyline.com</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>javmeindonesia / jakartapetexpo / unimedianorge</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>14-30</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Foreign event sites</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>skyline.com</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>teamster.org / uwaterloo.ca / fitnyc.edu / whosonthemove / greenbayinnovationgroup</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>28-88</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Job/member/directory pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>skyline.com</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>thewebhospitality.com</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>34</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Blog-comment spam list</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>skyline.com</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>bluleadz.com</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>70</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Sent via contact form</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>skyline.com</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>haasmarketing.co</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>29</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Solo consultant homepage</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>skyline.com</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>btsprod / tradegroup / adamexpostand</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>4-35</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Competitor - skipped</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Exhibit companies</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>skyline.com</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>leadiq / grokipedia / wikipedia</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>71-97</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Data profiles / encyclopedias</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>orbus.com</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>exhibitcitynews.com</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>56</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Sent (see tracker)</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Already contacted</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>orbus.com</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>marketing-mentor.com</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>62</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Association list, not vendors</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>orbus.com</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>theexhibitorshandbook / promohandbook / officesigncompany / fsdisplaysystems / speedprotradeshowdisplays / orbusvisualcommunicationsgroup / orbuscanada</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>1-34</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Orbus dealer catalog pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>orbus.com</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>signshop.com (Sign Builder Illustrated)</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>49</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Sent (see tracker)</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>amarcheschi@sbpub.com (Editor-in-Chief)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>orbus.com</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>exhibitoronline.com news</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>72</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Press-release coverage, not pitchable cold</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>orbus.com</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>scubefixtures.com</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>24</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Competitor - skipped</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Display manufacturer</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>orbus.com</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>narteamstore.realtor</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>38</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Realtor store</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>orbus.com</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>weareprintready.com</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>2</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Competitor - skipped</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Print shop</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>orbus.com</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>alinabradford.com</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>37</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Freelance writer blog</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>orbus.com</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>myeventweb.com</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>4</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Very low authority</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>orbus.com</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>members.asicentral.com</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>79</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>ASI members-only news</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>orbus.com</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>plumgroveinc.com / nimlok.com</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>29-44</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Competitor - skipped</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Competitors</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>xibitsolutions.com</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>gogather.com</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>34</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Sent (see tracker)</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Roundup inclusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>xibitsolutions.com</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>elev8.la</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>38</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Sent (see tracker)</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Partnership</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>xibitsolutions.com</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>bbb / crunchbase / lasvegasbusinessdirectory</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>9-93</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Profiles/directories</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>xibitsolutions.com</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>rifleconfigurator / theavidoutdoorsman / hoodline / webmobi</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>11-79</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Credit-line image links</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>xibitsolutions.com</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>alltopstartups / prweb / robinwaite / deliberatedirections / digitaljournal</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>58-90</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Old or paid-placement articles</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>xibitsolutions.com</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>siterankprovider / seoexpress / freepachecker / big-easy-seo / goldendreamoverseas</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>0-49</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>SEO spam</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>3dexhibits.com</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>thefreemancompany.com</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>35</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Competitor - skipped</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Exhibit company</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>3dexhibits.com</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>iprgezgini / firstclasslimos / lakesideplacecle</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>6-29</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Unrelated</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>3dexhibits.com</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>exhibitoradvocacy.com</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>28</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Sent (see tracker)</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Already contacted</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>3dexhibits.com</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>chicagotribune workplaces / hcea.org</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>39-90</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Awards / association events</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>3dexhibits.com</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>exhibitcitynews.com</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>56</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Sent (see tracker)</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Already contacted</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>3dexhibits.com</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>bizbash.com</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>79</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Sent (see tracker)</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>editorial@bizbash.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>3dexhibits.com</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>clearviewtvmirror.com</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>23</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Sent via contact form</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>3dexhibits.com</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>wearesparks.com</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>53</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Lead form only, no message field</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>3dexhibits.com</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>thebloggess.com / caileyreeddesigns.com</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>20-69</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Personal blogs</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>3dexhibits.com</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>interactiveparty.com</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>34</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Competitor - skipped</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Event entertainment vendor</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>3dexhibits.com</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>exhibitoronline.com</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>72</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Old article</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>3dexhibits.com</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>tradeshowlabs.com</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>56</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Sent (see tracker)</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>contact@tradeshowlabs.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>3dexhibits.com</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>blueatlasmarketing.com</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>46</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Sent (see tracker)</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Partnership / quote</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>3dexhibits.com</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>ezilon / contactout / leadiq</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>56-74</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Directories / data profiles</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>postergarden.com</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>displaydynamics.ca / displayboutique.ca</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>2-4</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>PosterGarden sister sites</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>postergarden.com</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>cappellaromana / trianglepro / rosecityhotclub</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>11-51</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Arts nonprofit sponsorships</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>postergarden.com</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>featherflagnation.com</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>42</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Competitor - skipped</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Flag/banner seller</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>postergarden.com</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>plumgroveinc.com</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>29</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Competitor - skipped</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Graphics supplier</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>postergarden.com</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>chambervu.com</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>51</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Chamber magazine ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>postergarden.com</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>grokipedia / accio / datanyze / siteprice</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>72-78</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AI/data aggregators</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>postergarden.com</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>mtmimagingsupplies.com</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>2</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Testimonial page</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>postergarden.com</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>print.wiki</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>21</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Glossary, no editorial contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>postergarden.com</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>right-space.com.sg / servicebureau.nl</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>4-9</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Foreign low authority</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>postergarden.com</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>andreawilsonwoods.com</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>13</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Personal blog</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>postergarden.com</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>insights4print.ceo</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>43</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Sent via contact form</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Submitted to Eddy Hagen</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>postergarden.com</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>agilitypr.com</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>78</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>PR SaaS vendor, not relevant outlet</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>postergarden.com</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>womensconference.org</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>40</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Low relevance</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>signazon.com</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>wikipedia / grokipedia / glassdoor / rocketreach</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>76-97</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Encyclopedias / profiles</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>signazon.com</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>simplycodes / dontpayfull</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>71-74</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Coupon aggregators</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>signazon.com</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>bmwblog / architekwiki / moneysavingexpert / lacar / detroittraining</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>25-84</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Off-topic citations</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>signazon.com</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>sg.utdallas.edu</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>82</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Student discount list</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>signazon.com</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>campaignsandelections.com</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>72</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Political yard signs, audience mismatch</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>signazon.com</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>mywahmplan / stylecarrot / art-collecting / grainedit / webdesignledger</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>7-74</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Old/low-relevance blogs</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>signazon.com</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>acquisition-international / entrepreneur.com</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>73-91</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Old paid/guest placements</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>impact-xm.com</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>engine.com</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>73</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>No contact form - support chat/phone only</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>impact-xm.com</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>propellant.media</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>52</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Sent (see tracker)</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Roundup inclusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>impact-xm.com</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>spotme.com</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>72</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Sent (see tracker)</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>americas@spotme.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>impact-xm.com</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>eventmarketer.com</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>76</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Sent (see tracker)</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Source relationship</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>impact-xm.com</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>jackmorton.com</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>66</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Competitor - skipped</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Agency (merged with Impact XM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>impact-xm.com</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>bizzabo.com</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>83</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Sent (see tracker)</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>blog@bizzabo.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>impact-xm.com</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>peninsulafunds / astriaelevate / agi-llc</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>4-24</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Investor portfolios</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>impact-xm.com</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>waze / yell / bizibl / dapralab</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>30-92</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Map/directory listings</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>impact-xm.com</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>globalfreestyle.com / evcom.org.uk</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>9-47</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Unrelated / UK awards</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>impact-xm.com</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>stova.io</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>78</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Partner page (event software)</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>impact-xm.com</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>avenuez.com</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>66</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Sent via contact form</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>impact-xm.com</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>eventindustrynews.com</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>69</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Sent (see tracker)</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Source relationship (editor@ from search result, not verified on-site)</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>impact-xm.com</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>prismlightinggroup.com</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>15</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Testimonial page</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>spiro.com</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>ges.com / 2heads.com / standoutwithspiro.com</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>3-71</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Spiro sister brands</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>spiro.com</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>getcontenttools.com / contentqueenmariah / salmanzafar.me / ellybowness / attilioreinhardt</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>1-46</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Unrelated or redirect artifacts</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>spiro.com</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>designrush.com</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>90</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Self-submit</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Manish to apply at designrush.com/submit/agency</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>spiro.com</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>ana.net</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>83</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Member-only list</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>spiro.com</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>revenuebase.ai</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>45</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Data aggregator</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>spiro.com</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>johnfarrellandassociates.com</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>1</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>M&amp;A consultancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>spiro.com</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>exhibitoronline.com (Find It)</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>72</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Paid marketplace listing</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>spiro.com</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>eventmeasurement.org</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>22</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Association</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>spiro.com</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>planet-water.org / insurtechny.com</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>50-57</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Unrelated</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>spiro.com</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>prnewswire / lbbonline</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>84-92</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Press releases</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>spiro.com</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>bizbash.com</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>79</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Sent (see tracker)</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>editorial@bizbash.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>derse.com</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>revenuebase.ai / himalayas / biztimes / standardresume / jtbworld</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>42-73</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Directories/profiles</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>derse.com</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>gacep.com / goprobriefings.com</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>15-34</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Unrelated partner lists</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>derse.com</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>exhibitoronline (Find It) / exhibitoradvocacy / exhibitcitynews</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>28-72</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Sent (see tracker)</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Already covered</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>derse.com</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>spectrum.rosco.com / tradegroup</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>35-70</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Competitor - skipped</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Vendor / competitor content</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>derse.com</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>fitnyc / unitedwaygmwc / ifesnet / thevalleymke / moonfruit / donahueadvisors</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>8-79</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Institutional/member pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>derse.com</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>blachreport.de / koschadepr.de</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>5-53</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>German-language press</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>ges.com</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>explace.on.ca / gameconcanada / ausa / wispa / myexpoexpo / iaee / informaconnect / aaoms / escardio / supplyside / asn-online</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>42-85</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Show organizer exhibitor-service links</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>ges.com</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>onpeak.com / theeventsgroup.ae / atozevents.com</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>2-71</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Competitor - skipped</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Event service companies</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>ges.com</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>gogather.com</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>34</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Sent (see tracker)</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Already contacted</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>ges.com</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>teamster988.org / ffvb.org</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>5-66</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Unrelated</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>ges.com</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>rockwayexhibits.com</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>21</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Competitor - skipped</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Exhibit company</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>ges.com</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>wikipedia (Poken)</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>97</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Encyclopedia</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>ges.com</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>thelogisticsoflogistics.com</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>49</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Needs manual submit</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Form filled; CAPTCHA checkbox needs Manish</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/outreach_tracker.xlsx
+++ b/outreach_tracker.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -534,7 +534,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1518,7 +1518,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Contact form (insights4print.ceo/contact)</t>
+          <t>eddy.hagen@insights4print.ceo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1765,12 +1765,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sent via contact form</t>
+          <t>REPLIED - sent detailed color-stability answer, offered a call</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1817,11 +1817,19 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Needs manual submit (CAPTCHA)</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
+          <t>Sent via contact form</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>marketing@apextradeshow.com</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
           <t>Form at trade-show-advisor.com/trade-show-advisor-contact-form.html requires ticking I'm-not-a-robot - Manish to submit</t>
@@ -1866,7 +1874,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1913,11 +1921,19 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Filled - needs manual CAPTCHA + submit</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
+          <t>Sent via contact form</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>marketing@apextradeshow.com</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr">
         <is>
           <t>Form is filled in on an open Chrome tab; Manish just ticks I'm-not-a-robot and clicks Submit</t>
@@ -1971,32 +1987,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Classic Exhibits</t>
+          <t>American Image Displays</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>exhibitoradvocacy.com</t>
+          <t>insurancecanopy.com</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>PR / Source relationship</t>
+          <t>Resource partnership / expert tip</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Joe Federbush (Founder)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>info@exhibitoradvocacy.com</t>
+          <t>info@insurancecanopy.com</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Supporting exhibitor-side transparency - from the print side</t>
+          <t>Same customers, different needs: vendor insurance + booth graphics</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2006,7 +2022,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2016,93 +2032,101 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Nonprofit exhibitor advocacy association; pitched as a printing-side source and asked about vendor alignment/listing</t>
+          <t>Insures market vendors/exhibitors (same customer base); site geo-blocked, email from search result</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Classic Exhibits</t>
+          <t>Vendor market outreach</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>scubefixtures.com</t>
+          <t>growingrootspartners.com (Craft + Mercantile night market, PA)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>N/A - competitor</t>
+          <t>Resource listing (vendor policy page)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Christy</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>christy@growingrootspartners.com</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>White 10x10 canopy tents for Craft + Mercantile vendors</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Skipped - competitor, not a partner</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>marketing@apextradeshow.com</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Actually a portable display/fixture manufacturer competing in adjacent hardware space, not a partnership fit</t>
+          <t>Vendor policy explicitly requires a white 10x10 canopy tent - no supplier named</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Xibit Solutions</t>
+          <t>Vendor market outreach</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>elev8.la</t>
+          <t>tempefestivalofthearts.com (Dec 4-6 2026)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Backlink / co-marketing partnership</t>
+          <t>Resource listing (FAQ page)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Grant Morningstar (CEO)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>hello@elev8.la</t>
+          <t>events@downtowntempe.com</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Booth staffing + booth graphics - referral partnership?</t>
+          <t>White canopy tents + booth signage for Dec 4-6 Tempe artists</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>REPLIED - wants our service list</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2112,39 +2136,39 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Event staffing/brand ambassador agency (Las Vegas) - complementary, non-competing service for the same exhibitors</t>
+          <t>FAQ prefers white tents w/ 40lb weights per leg for ~350 accepted artists twice a year</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Impact XM</t>
+          <t>Vendor market outreach</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>eventindustrynews.com</t>
+          <t>midwestcityok.org (Covered in Color)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>PR / Source relationship</t>
+          <t>Resource listing (application page)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Adam Parry (Editor)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>editor@eventindustrynews.com</t>
+          <t>SpecialEvents@MidwestCityOK.org</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Printing/production-side source for event industry stories</t>
+          <t>Tent + booth signage resource for Covered in Color vendors</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2154,7 +2178,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2164,24 +2188,24 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>UK event industry trade news site; address came from a search result, not listed on-site - watch for bounce</t>
+          <t>Vendor application strongly recommends own tent, tables, signage - no supplier named</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Impact XM</t>
+          <t>Vendor market outreach</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>engine.com</t>
+          <t>hudsonvalleyopenmarket.com (2026 vendor info)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>PR / Roundup inclusion</t>
+          <t>Resource listing (vendor info page)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2191,41 +2215,49 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>No form - support chat/phone only</t>
+          <t>hudsonvalleyopenmarket@gmail.com</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Tent + weights + banner resource for Hudson Valley vendors</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Skipped - no contact form exists</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>marketing@apextradeshow.com</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Sports event planning roundup; engine.com/contact-us</t>
+          <t>Vendor info requires 10x10 tent + 25lb weight per leg - specific setup, no supplier named</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Impact XM</t>
+          <t>Vendor market outreach</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>spotme.com</t>
+          <t>chiceventsdc.com (Royal Events Group, 16+ DC-area markets/yr)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Referral / resource partnership</t>
+          <t>Resource listing across event calendar</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2235,12 +2267,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>americas@spotme.com</t>
+          <t>ArtsandCrafts@Royal-EventsPlanning.com</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Partnership idea: SpotMe events + printed booth graphics</t>
+          <t>Tent + banner resource for your 16+ DC-area markets</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2250,7 +2282,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2260,39 +2292,39 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Enterprise event platform, 'best hybrid event management companies' roundup; spotme.com/contact-us</t>
+          <t>Runs National Harbor, Kentlands, Alexandria + other markets; vendors bring own tent, may hang booth signage</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Impact XM</t>
+          <t>E-Z UP</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>bizzabo.com</t>
+          <t>artsgoggle.org (Fort Worth art festival)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>PR / Blog feature</t>
+          <t>Resource listing (artist info page)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Blog team</t>
+          <t>Natalie Atkinson (Events + Projects Manager)</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>blog@bizzabo.com</t>
+          <t>natalie@nearsouthsidefw.org</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Feature idea: the printed side of corporate event themes</t>
+          <t>Booth tent + banner resource for ArtsGoggle artists</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2302,7 +2334,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2312,49 +2344,49 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Event platform, corporate event themes blog; bizzabo.com/contact-us</t>
+          <t>1,000+ artist booths, Oct 24 2026; artist-info page currently recommends E-Z UP tents</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Impact XM</t>
+          <t>Classic Exhibits</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>avenuez.com</t>
+          <t>exhibitoradvocacy.com</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>PR / Roundup inclusion</t>
+          <t>PR / Source relationship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Joe Federbush (Founder)</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Contact form (avenuez.com/contact-us)</t>
+          <t>info@exhibitoradvocacy.com</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Contact form: referral partnership / guide mention</t>
+          <t>Supporting exhibitor-side transparency - from the print side</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sent via contact form</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2364,34 +2396,34 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Beauty/wellness event PR agency, roundup lists Avenue Z itself first; avenuez.com/contact-us</t>
+          <t>Nonprofit exhibitor advocacy association; pitched as a printing-side source and asked about vendor alignment/listing</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3D Exhibits / Expo Marketing</t>
+          <t>Classic Exhibits</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>wearesparks.com</t>
+          <t>scubefixtures.com</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>PR / Source relationship</t>
+          <t>N/A - competitor</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Kristin Castelli (SVP Strategic Growth)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Lead form only - no message field</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2401,12 +2433,360 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Skipped - form cannot carry a message</t>
+          <t>Skipped - competitor, not a partner</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
+        <is>
+          <t>Actually a portable display/fixture manufacturer competing in adjacent hardware space, not a partnership fit</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Xibit Solutions</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>elev8.la</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Backlink / co-marketing partnership</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Grant Morningstar (CEO)</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>hello@elev8.la</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Booth staffing + booth graphics - referral partnership?</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Replied - service list sent, call proposed</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>marketing@apextradeshow.com</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Event staffing/brand ambassador agency (Las Vegas) - complementary, non-competing service for the same exhibitors</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Impact XM</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>eventindustrynews.com</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>PR / Source relationship</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Adam Parry (Editor)</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>editor@eventindustrynews.com</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Printing/production-side source for event industry stories</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>marketing@apextradeshow.com</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>UK event industry trade news site; address came from a search result, not listed on-site - watch for bounce</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Impact XM</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>engine.com</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>PR / Roundup inclusion</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>No form - support chat/phone only</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Skipped - no contact form exists</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Sports event planning roundup; engine.com/contact-us</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Impact XM</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>spotme.com</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Referral / resource partnership</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>americas@spotme.com</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Partnership idea: SpotMe events + printed booth graphics</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>marketing@apextradeshow.com</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Enterprise event platform, 'best hybrid event management companies' roundup; spotme.com/contact-us</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Impact XM</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>bizzabo.com</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>PR / Blog feature</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Blog team</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>blog@bizzabo.com</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Feature idea: the printed side of corporate event themes</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>marketing@apextradeshow.com</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Event platform, corporate event themes blog; bizzabo.com/contact-us</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Impact XM</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>avenuez.com</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>PR / Roundup inclusion</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Contact form (avenuez.com/contact-us)</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Contact form: referral partnership / guide mention</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Sent via contact form</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>marketing@apextradeshow.com</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Beauty/wellness event PR agency, roundup lists Avenue Z itself first; avenuez.com/contact-us</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>3D Exhibits / Expo Marketing</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>wearesparks.com</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>PR / Source relationship</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Kristin Castelli (SVP Strategic Growth)</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Lead form only - no message field</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Skipped - form cannot carry a message</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
         <is>
           <t>Global healthcare/experiential brand agency, appeared as referrer for both Expo Marketing and 3D Exhibits; wearesparks.com/contact/</t>
         </is>
@@ -2423,7 +2803,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2838,23 +3218,148 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>showdowndisplays.com</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>57</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>116K</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1.2K</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Wholesale tent/flag/banner supplier sold through promo distributors - backlinks are resellers' vendor-link pages (a wholesale/reseller channel, not editorial)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>vispronet.com</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>45</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>16K</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1.6K</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Online tent/banner printer - earns links from its own how-to guides (pride flags, sublimation, hanging banners) being cited; few outreach targets</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>american-image.com</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>43</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>241K</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1.6K</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Trade show exhibit company - strong content/expert-quote links (tip roundups, small-biz blogs, AI Journal, Insurance Canopy)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>tradeshowdisplaypros.com</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>9</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>5.1K</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>983</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Low authority; links are mostly paid guest posts on general blogs and competitor pages - nothing new to pitch</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ezup.com</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>52</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>18K</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2.8K</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Canopy tent brand - top links come from teacher/military/first-responder discount lists (VA News DR91, Parade DR85) and festival vendor-info pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>ges.com</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="B22" t="n">
         <v>71</v>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>59K</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>4.7K</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Global exhibition services giant - referrers mostly venues, associations, and exhibitor service portals (not editorial content); no new usable contacts found</t>
         </is>
@@ -2871,7 +3376,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E162"/>
+  <dimension ref="A1:E186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3869,12 +4374,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Needs manual submit</t>
+          <t>Sent via contact form</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Form has an I'm-not-a-robot CAPTCHA - Manish must submit</t>
+          <t>Confirmed - publisher Jules Sowder</t>
         </is>
       </c>
     </row>
@@ -7042,12 +7547,642 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Needs manual submit</t>
+          <t>Sent via contact form</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Form filled; CAPTCHA checkbox needs Manish</t>
+          <t>Confirmed by Joe Lynch auto-thanks</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>showdowndisplays.com</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>keystonead / majormktg / batcity / logoexpressions / joshowpromos / psprinting / prg.ca / doolittlesprintserve / bflprinting / signproiowa / prodesigns365</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>2-36</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Promo distributors' supplier pages - requires a wholesale program</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>showdowndisplays.com</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>flagpro / maximumpro / walloffameproducts / americanoutfitters / nifda.net</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>10-29</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Resellers / flag dealer association</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>showdowndisplays.com</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>members.asicentral.com / grokipedia / chemicalsamerica / printleaf</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>37-79</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>ASI members-only / aggregators / resellers</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>vispronet.com</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>vispronet.de / .at / .fr / .eu</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>3-34</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Own international sites</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>vispronet.com</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>wikipedia / wikihow / hunker / gemstonelights / matadormeggings / interestingfacts / artglasssupplies / lakeshorefablab</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>7-97</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Citations of Vispronet's blog guides - content, not outreach</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>vispronet.com</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>impact-nw.com</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>23</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Competitor - skipped</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Print shop</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>vispronet.com</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>simplycodes / saver / bbb</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>11-93</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Coupons / profiles</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>vispronet.com</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>adamchristing.com / ampddesigns / creekroadrentals / heartlandanimalshelter</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>6-34</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Low relevance</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>american-image.com</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>insurancecanopy.com</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>70</v>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Sent (see tracker)</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>info@insurancecanopy.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>american-image.com</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>tablelegsonline.com</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>31</v>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Expert-tip roundup but phone-only contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>american-image.com</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>zachwaldman.com</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>31</v>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Contact form / no public email</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Trade show magician - booking form only</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>american-image.com</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>badgermapping.com</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>68</v>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Contact form / no public email</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Sales software blog - contact form only</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>american-image.com</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>experiumagency.com</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>8</v>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Competitor - skipped</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>UK exhibition stand company</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>american-image.com</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>tradeshowlabs.com</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>57</v>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Sent (see tracker)</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Already contacted</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>american-image.com</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>wavecnct / noahpinion / voices / ahaslides / dunelandmedia / marketing-resultats / topleftdesign / carolroth / aijourn / lookwhatmomfound / olympiaartleague / grokipedia</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>12-78</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Citations of American Image's content, off-topic or low fit</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>american-image.com</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>exhibit-design-search / myshopify</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>56-95</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>American Image's own properties</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>tradeshowdisplaypros.com</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>anyvoo / vocal.media / 4mark / techbii / computertechreviews / teamgate / mikegingerich / logingit / metalplastikcelik / 1ptdesign</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>0-82</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Paid guest posts / off-topic</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>tradeshowdisplaypros.com</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>arrowheadsigncompany / displaystandsmarket / iconicdisplays / amitoje / vdshowcase</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>1-33</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Competitor - skipped</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Sign/display companies</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>tradeshowdisplaypros.com</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>print.wiki / sitelike / accio / alldatabases / yolasite</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>15-84</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Glossary / aggregators / own mirror</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>ezup.com</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>news.va.gov / parade / collegetransitions / teacherscan / dontpayfull</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>12-91</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Discount lists - need a teacher/military/first-responder discount program (Manish's decision)</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>ezup.com</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>artsgoggle.org</t>
+        </is>
+      </c>
+      <c r="C183" t="n">
+        <v>35</v>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Sent (see tracker)</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>natalie@nearsouthsidefw.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>ezup.com</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>ezup.nl / .ca / .eu / .fr / .de / adidas-team</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>19-55</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>E-Z UP's own sites / co-brand store</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>ezup.com</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>westshade.com</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>17</v>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Competitor - skipped</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Canopy competitor</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>ezup.com</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>swiftotter / hawksem / boast.io / cmc.com / pnw4wda / drinkluckyduck / simplycodes</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>0-75</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Agency case studies, coupons, off-topic</t>
         </is>
       </c>
     </row>
